--- a/public/materialapoyo/desglose_municipios.xlsx
+++ b/public/materialapoyo/desglose_municipios.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1724" uniqueCount="1157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1724" uniqueCount="1158">
   <si>
     <t>clave</t>
   </si>
@@ -3496,6 +3496,9 @@
   </si>
   <si>
     <t>Área enfoque atendida</t>
+  </si>
+  <si>
+    <t>SAN PEDRO MIXTEPEC_</t>
   </si>
 </sst>
 </file>
@@ -14811,7 +14814,7 @@
       <c r="H574" s="5"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="qYMet6ICxsieWL0lExwBsldVxyw0Kk/x8CYOsXaye73GkdENrIX2XWSjmb12ALEi+1rqNYaU7Xh7irIlMNrF0Q==" saltValue="DfD5MTqZLYfLNLuU2scNyA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="GrXxrrbyT3ne2VfPKx6q6saJKb4W3rq9nUo/GiBtCrOzPY2dP1eBQGeLupXxF4wt5jXSbiy0TQQU3QhRqP91CQ==" saltValue="bHsGoIeifIcm9Khs91KB6w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="4">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
@@ -18386,7 +18389,7 @@
         <v>515</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>514</v>
+        <v>1157</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>27</v>
